--- a/rule_review/templates/规则验证示例.xlsx
+++ b/rule_review/templates/规则验证示例.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务" sheetId="1" r:id="R4254eb4db11a40dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务事实" sheetId="2" r:id="R8d46dacb4e824c41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则台账" sheetId="3" r:id="R5d5624bd28434c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则条件" sheetId="4" r:id="R526bbddc740a4d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对照用例" sheetId="5" r:id="R30f43a36fb83434f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务" sheetId="1" r:id="R56e4417228664caf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务事实" sheetId="2" r:id="Re30a1d589be34304"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则台账" sheetId="3" r:id="R4be1d5bd409c463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则条件" sheetId="4" r:id="R4e0ce9690f0a43f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对照用例" sheetId="5" r:id="R202223cb30fb4495"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -41,12 +41,17 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF243B55"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -66,7 +71,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="13">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -91,6 +96,15 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1466,6 +1480,7 @@
     <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1481,6 +1496,9 @@
       <x:c r="D1" s="5" t="str">
         <x:v>预期规则状态</x:v>
       </x:c>
+      <x:c r="E1" s="12" t="str">
+        <x:v>预期需求结论</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -1495,6 +1513,9 @@
       <x:c r="D2" s="6" t="str">
         <x:v>pass</x:v>
       </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>归档能力</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="27" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -1509,6 +1530,9 @@
       <x:c r="D3" s="6" t="str">
         <x:v>pass</x:v>
       </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>快速复核能力</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1523,6 +1547,9 @@
       <x:c r="D4" s="6" t="str">
         <x:v>fail</x:v>
       </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>无结论</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -1537,6 +1564,9 @@
       <x:c r="D5" s="6" t="str">
         <x:v>fail</x:v>
       </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>无结论</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -1551,6 +1581,9 @@
       <x:c r="D6" s="6" t="str">
         <x:v>pass</x:v>
       </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>归档能力</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -1564,6 +1597,9 @@
       </x:c>
       <x:c r="D7" s="6" t="str">
         <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>无结论</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
@@ -1571,30 +1607,35 @@
       <x:c r="B8" s="2"/>
       <x:c r="C8" s="2"/>
       <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
       <x:c r="A9" s="2"/>
       <x:c r="B9" s="2"/>
       <x:c r="C9" s="2"/>
       <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
       <x:c r="A10" s="2"/>
       <x:c r="B10" s="2"/>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
       <x:c r="A11" s="2"/>
       <x:c r="B11" s="2"/>
       <x:c r="C11" s="2"/>
       <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="2"/>
       <x:c r="B12" s="2"/>
       <x:c r="C12" s="2"/>
       <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
